--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.88469741969001</v>
+        <v>8.431263330699627</v>
       </c>
       <c r="D2" t="n">
-        <v>51.62852298615302</v>
+        <v>8.389634985249865</v>
       </c>
       <c r="E2" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F2" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.99734809634282</v>
+        <v>7.962069065655708</v>
       </c>
       <c r="D3" t="n">
-        <v>42.61119521627401</v>
+        <v>6.924319222644526</v>
       </c>
       <c r="E3" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F3" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.93308594878817</v>
+        <v>6.651626466678078</v>
       </c>
       <c r="D4" t="n">
-        <v>40.67724102300448</v>
+        <v>6.610051666238228</v>
       </c>
       <c r="E4" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F4" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.91810494078152</v>
+        <v>8.111692052876997</v>
       </c>
       <c r="D5" t="n">
-        <v>43.89360091390113</v>
+        <v>7.132710148508934</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F5" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.83288695566154</v>
+        <v>5.497844130295001</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71658703486901</v>
+        <v>5.153945393166215</v>
       </c>
       <c r="E6" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F6" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.74837735363328</v>
+        <v>7.271611319965408</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32380837442437</v>
+        <v>6.22761886084396</v>
       </c>
       <c r="E7" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F7" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.87962927890499</v>
+        <v>8.267939757822061</v>
       </c>
       <c r="D8" t="n">
-        <v>30.16853757644301</v>
+        <v>4.902387356171989</v>
       </c>
       <c r="E8" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F8" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.18473037303773</v>
+        <v>7.992518685618632</v>
       </c>
       <c r="D9" t="n">
-        <v>37.35362385800534</v>
+        <v>6.069963876925868</v>
       </c>
       <c r="E9" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F9" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80169041476533</v>
+        <v>8.742774692399367</v>
       </c>
       <c r="D10" t="n">
-        <v>21.53819978692773</v>
+        <v>3.499957465375756</v>
       </c>
       <c r="E10" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F10" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.193980008652028</v>
+        <v>0.8440217514059546</v>
       </c>
       <c r="D11" t="n">
-        <v>8.645571800237148</v>
+        <v>1.404905417538537</v>
       </c>
       <c r="E11" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F11" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.10101039048578</v>
+        <v>2.94141418845394</v>
       </c>
       <c r="D12" t="n">
-        <v>12.84237741712715</v>
+        <v>2.086886330283162</v>
       </c>
       <c r="E12" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F12" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.13721385814401</v>
+        <v>7.822297251948402</v>
       </c>
       <c r="D13" t="n">
-        <v>14.60469877973559</v>
+        <v>2.373263551707034</v>
       </c>
       <c r="E13" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F13" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.57673198013495</v>
+        <v>4.31871894677193</v>
       </c>
       <c r="D14" t="n">
-        <v>27.01765915949206</v>
+        <v>4.390369613417459</v>
       </c>
       <c r="E14" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F14" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.28552729928451</v>
+        <v>4.433898186133733</v>
       </c>
       <c r="D15" t="n">
-        <v>14.02128676610145</v>
+        <v>2.278459099491485</v>
       </c>
       <c r="E15" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F15" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>39.86261127645525</v>
+        <v>6.477674332423979</v>
       </c>
       <c r="D16" t="n">
-        <v>25.56565846665526</v>
+        <v>4.154419500831479</v>
       </c>
       <c r="E16" t="n">
-        <v>13.82449794631811</v>
+        <v>2.246480916276693</v>
       </c>
       <c r="F16" t="n">
-        <v>12.64177620683363</v>
+        <v>2.054288633610466</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
